--- a/layout/Layout CF_V3_CF_I.xlsx
+++ b/layout/Layout CF_V3_CF_I.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4c8ce57d2d00b7c/Documentos/Stagged/ION/Analisis/02_CF_ESP_progress/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{024B4D83-01F3-4B98-BA2B-C44575E7A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B5D9FAA-A686-4E15-B2F6-6BD4ED1B3522}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0226AAD4-8561-4D4A-9295-727728465E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5950" yWindow="4120" windowWidth="26760" windowHeight="15170" xr2:uid="{5F6E1A63-E6C9-4504-B23A-16F4EB37FB45}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{5F6E1A63-E6C9-4504-B23A-16F4EB37FB45}"/>
   </bookViews>
   <sheets>
     <sheet name="CF ESP" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>ORDEN</t>
   </si>
@@ -80,18 +80,12 @@
     <t>Tipo de Operación</t>
   </si>
   <si>
-    <t>Anexo 1</t>
-  </si>
-  <si>
     <t>TIPOFONDEO</t>
   </si>
   <si>
     <t>Tipo de Fondeo</t>
   </si>
   <si>
-    <t>Anexo 5</t>
-  </si>
-  <si>
     <t>FECHA_INICIO</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>CVE_ACREEDOR</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>Clave del acreedor, conforme al formulario de contrapartes</t>
   </si>
   <si>
@@ -146,9 +137,6 @@
     <t>Tipo de relación del acreditado</t>
   </si>
   <si>
-    <t>Anexo 4</t>
-  </si>
-  <si>
     <t>CVE_OPERACION</t>
   </si>
   <si>
@@ -156,13 +144,25 @@
   </si>
   <si>
     <t>Clave de identificación (folio) de la operación</t>
+  </si>
+  <si>
+    <t>MONEDA ISO</t>
+  </si>
+  <si>
+    <t>TIPO OPERACION CF I</t>
+  </si>
+  <si>
+    <t>TIPO FONDEO CF I</t>
+  </si>
+  <si>
+    <t>TIPO RELACION ACREDITADO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -174,31 +174,18 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="8"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,41 +194,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3"/>
+        <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -266,28 +226,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,314 +566,256 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA2AFDD3-706E-4EA1-BC2E-60901856D1E6}">
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="12.5" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1796875" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" customWidth="1"/>
-    <col min="5" max="5" width="4.7265625" customWidth="1"/>
-    <col min="6" max="6" width="46.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="6.7265625" customWidth="1"/>
-    <col min="13" max="13" width="18.54296875" customWidth="1"/>
-    <col min="14" max="256" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.88671875" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="254" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2">
         <v>6</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="B10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="F10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <f>A8+1</f>
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="17" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <f>A9+1</f>
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-    </row>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
